--- a/Template/DanhSachGoiThau.xlsx
+++ b/Template/DanhSachGoiThau.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DanhSachGoiThau" sheetId="1" r:id="rId1"/>
-    <sheet name="STT" sheetId="2" r:id="rId2"/>
+    <sheet name="Detail" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
   <si>
     <t>STT</t>
   </si>
@@ -1791,232 +1791,232 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="27.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="36.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="37.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="45.4285714285714" customWidth="1"/>
-    <col min="6" max="8" width="46.1428571428571" customWidth="1"/>
-    <col min="9" max="9" width="37" customWidth="1"/>
-    <col min="10" max="11" width="45.7142857142857" customWidth="1"/>
-    <col min="12" max="12" width="41" customWidth="1"/>
-    <col min="13" max="13" width="28.1428571428571" customWidth="1"/>
-    <col min="14" max="14" width="27.5714285714286" customWidth="1"/>
-    <col min="15" max="15" width="27.8571428571429" customWidth="1"/>
-    <col min="16" max="16" width="37.1428571428571" customWidth="1"/>
-    <col min="17" max="17" width="28.4285714285714" customWidth="1"/>
-    <col min="18" max="18" width="27.8571428571429" customWidth="1"/>
-    <col min="19" max="19" width="27.5714285714286" customWidth="1"/>
-    <col min="20" max="20" width="27.7142857142857" customWidth="1"/>
-    <col min="21" max="21" width="19.5714285714286" customWidth="1"/>
-    <col min="22" max="22" width="18.7142857142857" customWidth="1"/>
-    <col min="25" max="25" width="28.1428571428571" customWidth="1"/>
-    <col min="26" max="26" width="27.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="27.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="36.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="37.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="45.4285714285714" customWidth="1"/>
+    <col min="7" max="9" width="46.1428571428571" customWidth="1"/>
+    <col min="10" max="10" width="37" customWidth="1"/>
+    <col min="11" max="12" width="45.7142857142857" customWidth="1"/>
+    <col min="13" max="13" width="41" customWidth="1"/>
+    <col min="14" max="14" width="28.1428571428571" customWidth="1"/>
+    <col min="15" max="15" width="27.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="27.8571428571429" customWidth="1"/>
+    <col min="17" max="17" width="37.1428571428571" customWidth="1"/>
+    <col min="18" max="18" width="28.4285714285714" customWidth="1"/>
+    <col min="19" max="19" width="27.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="27.5714285714286" customWidth="1"/>
+    <col min="21" max="21" width="27.7142857142857" customWidth="1"/>
+    <col min="22" max="22" width="19.5714285714286" customWidth="1"/>
+    <col min="23" max="23" width="18.7142857142857" customWidth="1"/>
+    <col min="26" max="26" width="28.1428571428571" customWidth="1"/>
+    <col min="27" max="27" width="27.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:37">
+    <row r="1" s="1" customFormat="1" spans="1:38">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
-      <c r="A2" s="3" t="s">
-        <v>80</v>
-      </c>
+    <row r="2" spans="2:38">
       <c r="B2" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>80</v>
       </c>
       <c r="T2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="X2" s="3" t="s">
         <v>80</v>
       </c>
       <c r="Y2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="AD2" s="3" t="s">
         <v>80</v>
@@ -2025,21 +2025,24 @@
         <v>80</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AG2" s="3" t="s">
         <v>96</v>
       </c>
       <c r="AH2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AK2" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AL2" s="3" t="s">
         <v>100</v>
       </c>
     </row>

--- a/Template/DanhSachGoiThau.xlsx
+++ b/Template/DanhSachGoiThau.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
+    <workbookView windowWidth="14400" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="DanhSachGoiThau" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
   <si>
     <t>STT</t>
   </si>
@@ -162,6 +162,9 @@
     <t>https://dauthau.asia/thongbao/moithau/goi-thau-so-3-so-hoa-tai-lieu-luu-tru-lich-su-tinh-hung-yen-giai-doan-2025-2030-1724486.html</t>
   </si>
   <si>
+    <t>Kế hoạch</t>
+  </si>
+  <si>
     <t>Trạng thái gói thầu</t>
   </si>
   <si>
@@ -183,6 +186,9 @@
     <t>Phân loại KHLCNT</t>
   </si>
   <si>
+    <t>Trong nước/Quốc tế</t>
+  </si>
+  <si>
     <t>Chi tiết nguồn vốn</t>
   </si>
   <si>
@@ -202,6 +208,9 @@
   </si>
   <si>
     <t>Thực hiện tại</t>
+  </si>
+  <si>
+    <t>Các thông báo liên quan</t>
   </si>
   <si>
     <t>Thời điểm đóng thầu</t>
@@ -502,7 +511,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,6 +526,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -696,12 +711,42 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -828,7 +873,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -840,127 +885,131 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1513,274 +1562,274 @@
   <dimension ref="A1:AG16"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="34.8571428571429" style="4" customWidth="1"/>
-    <col min="3" max="3" width="57.4285714285714" style="4" customWidth="1"/>
-    <col min="4" max="4" width="44" style="5" customWidth="1"/>
-    <col min="5" max="5" width="34.4285714285714" style="4" customWidth="1"/>
-    <col min="6" max="6" width="134" style="4" customWidth="1"/>
-    <col min="7" max="7" width="26.8571428571429" style="4" customWidth="1"/>
-    <col min="8" max="8" width="30.7142857142857" style="4" customWidth="1"/>
+    <col min="2" max="2" width="34.8571428571429" style="8" customWidth="1"/>
+    <col min="3" max="3" width="57.4285714285714" style="8" customWidth="1"/>
+    <col min="4" max="4" width="44" style="9" customWidth="1"/>
+    <col min="5" max="5" width="34.4285714285714" style="8" customWidth="1"/>
+    <col min="6" max="6" width="134" style="8" customWidth="1"/>
+    <col min="7" max="7" width="26.8571428571429" style="8" customWidth="1"/>
+    <col min="8" max="8" width="30.7142857142857" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:33">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="U2" s="9"/>
-      <c r="AG2" s="9"/>
+      <c r="U2" s="13"/>
+      <c r="AG2" s="13"/>
     </row>
     <row r="3" spans="1:33">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="9"/>
+      <c r="F3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="9"/>
-      <c r="AG3" s="9"/>
+      <c r="U3" s="13"/>
+      <c r="AG3" s="13"/>
     </row>
     <row r="4" spans="1:33">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="U4" s="9"/>
-      <c r="AG4" s="9"/>
+      <c r="U4" s="13"/>
+      <c r="AG4" s="13"/>
     </row>
     <row r="5" spans="1:33">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="9"/>
+      <c r="F5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="U5" s="9"/>
-      <c r="AG5" s="9"/>
+      <c r="U5" s="13"/>
+      <c r="AG5" s="13"/>
     </row>
     <row r="6" spans="1:33">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="U6" s="9"/>
-      <c r="AG6" s="9"/>
+      <c r="U6" s="13"/>
+      <c r="AG6" s="13"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:30">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="11">
         <v>46298.6666666667</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="Z10" s="9"/>
-      <c r="AD10" s="9"/>
+      <c r="Z10" s="13"/>
+      <c r="AD10" s="13"/>
     </row>
     <row r="11" spans="1:30">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="11">
         <v>46298.6131944444</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="Z11" s="9"/>
-      <c r="AD11" s="9"/>
+      <c r="Z11" s="13"/>
+      <c r="AD11" s="13"/>
     </row>
     <row r="12" spans="1:30">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="11">
         <v>46298.60625</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
+      <c r="E12" s="9"/>
+      <c r="F12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Z12" s="9"/>
-      <c r="AD12" s="9"/>
+      <c r="Z12" s="13"/>
+      <c r="AD12" s="13"/>
     </row>
     <row r="13" spans="1:30">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="11">
         <v>46268.6965277778</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="9"/>
+      <c r="F13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="Z13" s="9"/>
-      <c r="AD13" s="9"/>
+      <c r="H13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="Z13" s="13"/>
+      <c r="AD13" s="13"/>
     </row>
     <row r="14" spans="1:33">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="11">
         <v>46056.6840277778</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5" t="s">
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="U14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AD14" s="9"/>
-      <c r="AG14" s="9"/>
+      <c r="H14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="U14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AG14" s="13"/>
     </row>
     <row r="15" spans="1:33">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="U15" s="9"/>
-      <c r="AG15" s="9"/>
+      <c r="U15" s="13"/>
+      <c r="AG15" s="13"/>
     </row>
     <row r="16" spans="1:33">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
+      <c r="E16" s="9"/>
+      <c r="F16" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="U16" s="9"/>
-      <c r="AG16" s="9"/>
+      <c r="U16" s="13"/>
+      <c r="AG16" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1791,33 +1840,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="27.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="36.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="37.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="45.4285714285714" customWidth="1"/>
-    <col min="7" max="9" width="46.1428571428571" customWidth="1"/>
-    <col min="10" max="10" width="37" customWidth="1"/>
-    <col min="11" max="12" width="45.7142857142857" customWidth="1"/>
-    <col min="13" max="13" width="41" customWidth="1"/>
-    <col min="14" max="14" width="28.1428571428571" customWidth="1"/>
-    <col min="15" max="15" width="27.5714285714286" customWidth="1"/>
-    <col min="16" max="16" width="27.8571428571429" customWidth="1"/>
-    <col min="17" max="17" width="37.1428571428571" customWidth="1"/>
-    <col min="18" max="18" width="28.4285714285714" customWidth="1"/>
+    <col min="3" max="5" width="27.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="36.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="37.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="45.4285714285714" customWidth="1"/>
+    <col min="9" max="11" width="46.1428571428571" customWidth="1"/>
+    <col min="12" max="13" width="37" customWidth="1"/>
+    <col min="14" max="15" width="45.7142857142857" customWidth="1"/>
+    <col min="16" max="16" width="41" customWidth="1"/>
+    <col min="17" max="17" width="28.1428571428571" customWidth="1"/>
+    <col min="18" max="18" width="27.5714285714286" customWidth="1"/>
     <col min="19" max="19" width="27.8571428571429" customWidth="1"/>
-    <col min="20" max="20" width="27.5714285714286" customWidth="1"/>
-    <col min="21" max="21" width="27.7142857142857" customWidth="1"/>
-    <col min="22" max="22" width="19.5714285714286" customWidth="1"/>
-    <col min="23" max="23" width="18.7142857142857" customWidth="1"/>
-    <col min="26" max="26" width="28.1428571428571" customWidth="1"/>
-    <col min="27" max="27" width="27.1428571428571" customWidth="1"/>
+    <col min="20" max="21" width="37.1428571428571" customWidth="1"/>
+    <col min="22" max="22" width="28.4285714285714" customWidth="1"/>
+    <col min="23" max="23" width="27.8571428571429" customWidth="1"/>
+    <col min="24" max="24" width="27.5714285714286" customWidth="1"/>
+    <col min="25" max="25" width="27.7142857142857" customWidth="1"/>
+    <col min="26" max="26" width="19.5714285714286" customWidth="1"/>
+    <col min="27" max="27" width="18.7142857142857" customWidth="1"/>
+    <col min="30" max="30" width="28.1428571428571" customWidth="1"/>
+    <col min="31" max="31" width="27.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:38">
+    <row r="1" s="1" customFormat="1" spans="1:42">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1827,223 +1876,239 @@
       <c r="C1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="7" t="s">
         <v>79</v>
       </c>
+      <c r="AN1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="2" spans="2:38">
-      <c r="B2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="3" t="s">
+    <row r="2" spans="2:42">
+      <c r="B2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="I2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="S2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="U2" s="3" t="s">
+      <c r="S2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="T2" s="4"/>
+      <c r="U2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="V2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="X2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z2" s="3" t="s">
+      <c r="W2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AE2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AF2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AL2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM2" s="4" t="s">
         <v>100</v>
+      </c>
+      <c r="AN2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP2" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Template/DanhSachGoiThau.xlsx
+++ b/Template/DanhSachGoiThau.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DanhSachGoiThau" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
   <si>
     <t>STT</t>
   </si>
@@ -84,84 +84,6 @@
     <t>https://dauthau.asia/thongbao/moithau/so-hoa-va-tao-lap-co-so-du-lieu-tai-lieu-luu-tru-giay-cua-cap-huyen-da-ket-thuc-hoat-dong-1730453.html</t>
   </si>
   <si>
-    <t>Gói thầu số 03: Cung cấp dịch vụ chỉnh lý, số hóa hồ sơ lưu trữ năm 2025-2026</t>
-  </si>
-  <si>
-    <t>14:25 19/03/2026</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/goi-thau-so-03-cung-cap-dich-vu-chinh-ly-so-hoa-ho-so-luu-tru-nam-2025-2026-1730079.html</t>
-  </si>
-  <si>
-    <t>Số hóa, nhập dữ liệu hồ sơ đơn, kết quả xử lý đơn vào cơ sở dữ liệu</t>
-  </si>
-  <si>
-    <t>16:01 17/03/2026</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/so-hoa-nhap-du-lieu-ho-so-don-ket-qua-xu-ly-don-vao-co-so-du-lieu-1729338.html</t>
-  </si>
-  <si>
-    <t>Gói thầu số 03: Thuê dịch vụ chỉnh lý, số hóa tài liệu lưu trữ của UBND phường Hà Lầm</t>
-  </si>
-  <si>
-    <t>10:04 17/03/2026</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/goi-thau-so-03-thue-dich-vu-chinh-ly-so-hoa-tai-lieu-luu-tru-cua-ubnd-phuong-ha-lam-1729090.html</t>
-  </si>
-  <si>
-    <t>Chỉnh lý tài liệu lưu trữ; chuẩn hóa, chuyển đổi và số hóa tài liệu lưu trữ</t>
-  </si>
-  <si>
-    <t>14:34 13/03/2026</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/chinh-ly-tai-lieu-luu-tru-chuan-hoa-chuyen-doi-va-so-hoa-tai-lieu-luu-tru-1728260.html</t>
-  </si>
-  <si>
-    <t>Gói thầu số 01: Số hóa tài liệu quản lý đất đai cấp huyện thuộc tỉnh Lào Cai cũ</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/goi-thau-so-01-so-hoa-tai-lieu-quan-ly-dat-dai-cap-huyen-thuoc-tinh-lao-cai-cu-1727041.html</t>
-  </si>
-  <si>
-    <t>Chỉnh lý và số hóa hồ sơ, tài liệu tại 05 xã, phường (cũ) được tiếp nhận, quản lý tại phường Hà Giang 2</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/chinh-ly-va-so-hoa-ho-so-tai-lieu-tai-05-xa-phuong-cu-duoc-tiep-nhan-quan-ly-tai-phuong-ha-giang-2-1726943.html</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/goi-thau-so-03-thue-dich-vu-chinh-ly-so-hoa-tai-lieu-luu-tru-cua-ubnd-phuong-ha-lam-1726938.html</t>
-  </si>
-  <si>
-    <t>Số hóa tài liệu lưu trữ của cơ quan cấp huyện sau sắp xếp tổ chức bộ máy năm 2025 của Sở Nội vụ</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/so-hoa-tai-lieu-luu-tru-cua-co-quan-cap-huyen-sau-sap-xep-to-chuc-bo-may-nam-2025-cua-so-noi-vu-1726701.html</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/so-hoa-tai-lieu-luu-tru-cua-co-quan-cap-huyen-sau-sap-xep-to-chuc-bo-may-nam-2025-cua-so-noi-vu-1724747.html</t>
-  </si>
-  <si>
-    <t>Chỉnh lý tài liệu lưu trữ và số hóa tài liệu tại Sở Xây dựng</t>
-  </si>
-  <si>
-    <t>18:03 28/02/2026</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/chinh-ly-tai-lieu-luu-tru-va-so-hoa-tai-lieu-tai-so-xay-dung-1724500.html</t>
-  </si>
-  <si>
-    <t>Gói thầu số 3: Số hóa tài liệu lưu trữ lịch sử tỉnh Hưng Yên giai đoạn 2025 - 2030</t>
-  </si>
-  <si>
-    <t>16:04 28/02/2026</t>
-  </si>
-  <si>
-    <t>https://dauthau.asia/thongbao/moithau/goi-thau-so-3-so-hoa-tai-lieu-luu-tru-lich-su-tinh-hung-yen-giai-doan-2025-2030-1724486.html</t>
-  </si>
-  <si>
     <t>Kế hoạch</t>
   </si>
   <si>
@@ -265,6 +187,9 @@
   </si>
   <si>
     <t>Kết quả lựa chọn nhà thầu</t>
+  </si>
+  <si>
+    <t>Giá trúng thầu (VND)</t>
   </si>
   <si>
     <t>Hình thức đảm bảo dự thầu</t>
@@ -511,7 +436,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -527,6 +452,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,7 +804,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -897,16 +828,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
@@ -915,85 +846,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1007,9 +938,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1658,122 +1589,74 @@
     <row r="6" spans="1:33">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>19</v>
-      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="9"/>
-      <c r="F6" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="F6" s="9"/>
       <c r="U6" s="13"/>
       <c r="AG6" s="13"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>22</v>
-      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="9" t="s">
-        <v>23</v>
-      </c>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>28</v>
-      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:30">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="11">
-        <v>46298.6666666667</v>
-      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="11"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="F10" s="9"/>
       <c r="Z10" s="13"/>
       <c r="AD10" s="13"/>
     </row>
     <row r="11" spans="1:30">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="11">
-        <v>46298.6131944444</v>
-      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="11"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="F11" s="9"/>
       <c r="Z11" s="13"/>
       <c r="AD11" s="13"/>
     </row>
     <row r="12" spans="1:30">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="11">
-        <v>46298.60625</v>
-      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="11"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="F12" s="9"/>
       <c r="Z12" s="13"/>
       <c r="AD12" s="13"/>
     </row>
     <row r="13" spans="1:30">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="11">
-        <v>46268.6965277778</v>
-      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="F13" s="9"/>
       <c r="H13" s="12"/>
       <c r="N13" s="12"/>
       <c r="Z13" s="13"/>
@@ -1782,16 +1665,10 @@
     <row r="14" spans="1:33">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="11">
-        <v>46056.6840277778</v>
-      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="11"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="F14" s="9"/>
       <c r="H14" s="12"/>
       <c r="N14" s="12"/>
       <c r="U14" s="13"/>
@@ -1802,32 +1679,20 @@
     <row r="15" spans="1:33">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="F15" s="9"/>
       <c r="U15" s="13"/>
       <c r="AG15" s="13"/>
     </row>
     <row r="16" spans="1:33">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>42</v>
-      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="9" t="s">
-        <v>43</v>
-      </c>
+      <c r="F16" s="9"/>
       <c r="U16" s="13"/>
       <c r="AG16" s="13"/>
     </row>
@@ -1840,7 +1705,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -1864,9 +1729,11 @@
     <col min="27" max="27" width="18.7142857142857" customWidth="1"/>
     <col min="30" max="30" width="28.1428571428571" customWidth="1"/>
     <col min="31" max="31" width="27.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="27.4285714285714" customWidth="1"/>
+    <col min="39" max="39" width="27.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:42">
+    <row r="1" s="1" customFormat="1" spans="1:43">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1874,241 +1741,245 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="AF1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="AG1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="AH1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="AI1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="AK1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="AL1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="AM1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="AN1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="AO1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="AP1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="2" t="s">
+    </row>
+    <row r="2" spans="2:43">
+      <c r="B2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK1" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM1" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP1" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="2:42">
-      <c r="B2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="L2" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="L2" s="4"/>
       <c r="M2" s="4" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="T2" s="4"/>
       <c r="U2" s="4" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="AD2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AM2" s="4" t="s">
-        <v>100</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="AM2" s="4"/>
       <c r="AN2" s="4" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="AP2" s="4" t="s">
-        <v>103</v>
+        <v>77</v>
+      </c>
+      <c r="AQ2" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
